--- a/artfynd/A 31295-2022 artfynd.xlsx
+++ b/artfynd/A 31295-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31295-2022 artfynd.xlsx
+++ b/artfynd/A 31295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60617914</v>
+        <v>60617913</v>
       </c>
       <c r="B2" t="n">
-        <v>44624</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -735,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullen, Öl</t>
+          <t>S Kullen, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621974.237769463</v>
+        <v>621974</v>
       </c>
       <c r="R2" t="n">
-        <v>6345972.920043187</v>
+        <v>6345748</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -784,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -803,7 +798,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vall med sand i kanterna</t>
+          <t>Vall med mycket sand utmed kanterna</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -818,6 +813,151 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>ÅGP Skärrande gräshoppa N Öland (Calluna_OKL0003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>60617914</v>
+      </c>
+      <c r="B3" t="n">
+        <v>45347</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101819</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skärrande gräshoppa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Stauroderus scalaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fischer-Waldheim, 1846)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kullen, Öl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>621974</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6345973</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-07-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-07-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mycket hög täthet</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vall med sand i kanterna</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Oskar Kindvall</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Oskar Kindvall, Malin Strand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>ÅGP Skärrande gräshoppa N Öland (Calluna_OKL0003)</t>
         </is>

--- a/artfynd/A 31295-2022 artfynd.xlsx
+++ b/artfynd/A 31295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
           <t>ÅGP Skärrande gräshoppa N Öland (Calluna_OKL0003)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60617913</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -962,8 +972,17 @@
           <t>ÅGP Skärrande gräshoppa N Öland (Calluna_OKL0003)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60617914</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>